--- a/ELTON/MATRIX DE DADOS_NOVA.xlsx
+++ b/ELTON/MATRIX DE DADOS_NOVA.xlsx
@@ -2399,6 +2399,12 @@
     <xf numFmtId="1" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2413,12 +2419,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="19" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2794,118 +2794,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
+      <c r="B2" s="22"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="27"/>
+      <c r="B4" s="22"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="25"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="27"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="27"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="25"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="27"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="28">
         <v>36344</v>
       </c>
@@ -2918,598 +2918,598 @@
       <c r="J11" s="30"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="27"/>
+      <c r="B14" s="22"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24"/>
+      <c r="C15" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="27"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="25"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="27"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="25"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="27"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="25"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="27"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="25"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="27"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23" t="s">
+      <c r="B23" s="24"/>
+      <c r="C23" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="25"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="27"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="25"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="27"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="25"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="27"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="25"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="27"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="25"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="27"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="25"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="27"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="22"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23" t="s">
+      <c r="B32" s="24"/>
+      <c r="C32" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="27"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="23" t="s">
+      <c r="B33" s="24"/>
+      <c r="C33" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="25"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="27"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="23" t="s">
+      <c r="B34" s="24"/>
+      <c r="C34" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="25"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="27"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23" t="s">
+      <c r="B35" s="24"/>
+      <c r="C35" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="25"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="27"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23" t="s">
+      <c r="B36" s="24"/>
+      <c r="C36" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="27"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23" t="s">
+      <c r="B37" s="24"/>
+      <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="25"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="27"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23" t="s">
+      <c r="B38" s="24"/>
+      <c r="C38" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="25"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="27"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="23" t="s">
+      <c r="B39" s="24"/>
+      <c r="C39" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="25"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="27"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23" t="s">
+      <c r="B40" s="24"/>
+      <c r="C40" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="25"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="27"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="23" t="s">
+      <c r="B41" s="24"/>
+      <c r="C41" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="25"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="27"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="23" t="s">
+      <c r="B42" s="24"/>
+      <c r="C42" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="25"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="27"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="23" t="s">
+      <c r="B43" s="24"/>
+      <c r="C43" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="25"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="27"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23" t="s">
+      <c r="B44" s="24"/>
+      <c r="C44" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="27"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="22"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="23" t="s">
+      <c r="B49" s="24"/>
+      <c r="C49" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="25"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="27"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23" t="s">
+      <c r="B50" s="24"/>
+      <c r="C50" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="25"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="27"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="22"/>
-      <c r="C51" s="23" t="s">
+      <c r="B51" s="24"/>
+      <c r="C51" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="25"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="27"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B52" s="22"/>
-      <c r="C52" s="23" t="s">
+      <c r="B52" s="24"/>
+      <c r="C52" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="25"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="27"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="23" t="s">
+      <c r="B53" s="24"/>
+      <c r="C53" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="25"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="27"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="23" t="s">
+      <c r="B54" s="24"/>
+      <c r="C54" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="25"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="27"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B55" s="22"/>
-      <c r="C55" s="23" t="s">
+      <c r="B55" s="24"/>
+      <c r="C55" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="25"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="27"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="23" t="s">
+      <c r="B56" s="24"/>
+      <c r="C56" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="25"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="27"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23" t="s">
+      <c r="B57" s="24"/>
+      <c r="C57" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="25"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
     </row>
     <row r="61" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
@@ -24667,12 +24667,78 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:J56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:J57"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:J53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:J54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:J55"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:J51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:J52"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:J40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:J41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:J39"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="A7:B7"/>
@@ -24686,78 +24752,12 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C11:J11"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:J33"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:J32"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:J35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:J37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:J38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:J39"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:J49"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:J40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:J41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:J50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:J51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:J52"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:J56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:J57"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:J53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:J54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:J55"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>
